--- a/毛利测算表2026.xlsx
+++ b/毛利测算表2026.xlsx
@@ -242,177 +242,180 @@
     <t>BSP驱动工程师</t>
   </si>
   <si>
+    <t>月度</t>
+  </si>
+  <si>
+    <t>中级</t>
+  </si>
+  <si>
+    <t>南昌</t>
+  </si>
+  <si>
+    <t>ITO</t>
+  </si>
+  <si>
+    <t>事业三部</t>
+  </si>
+  <si>
+    <t>汤文杰</t>
+  </si>
+  <si>
+    <t>方龙翔</t>
+  </si>
+  <si>
+    <t>张**</t>
+  </si>
+  <si>
+    <t>诗悦</t>
+  </si>
+  <si>
+    <t>camera tuning工程师</t>
+  </si>
+  <si>
+    <t>上海</t>
+  </si>
+  <si>
+    <t>事业六部</t>
+  </si>
+  <si>
+    <t>陈搏</t>
+  </si>
+  <si>
+    <t>聂岑楠</t>
+  </si>
+  <si>
+    <t>苏**</t>
+  </si>
+  <si>
+    <t>上海海橘</t>
+  </si>
+  <si>
+    <t>小米</t>
+  </si>
+  <si>
+    <t>路测驾驶员</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>BPO</t>
+  </si>
+  <si>
+    <t>社保缴纳地</t>
+  </si>
+  <si>
+    <t>不缴纳</t>
+  </si>
+  <si>
+    <t>最低社保</t>
+  </si>
+  <si>
+    <t>最低公积金</t>
+  </si>
+  <si>
+    <t>级别</t>
+  </si>
+  <si>
+    <t>回款方式</t>
+  </si>
+  <si>
+    <t>资金费率</t>
+  </si>
+  <si>
+    <t>助理</t>
+  </si>
+  <si>
+    <t>安硕</t>
+  </si>
+  <si>
+    <t>半年度</t>
+  </si>
+  <si>
+    <t>南京</t>
+  </si>
+  <si>
+    <t>初级</t>
+  </si>
+  <si>
+    <t>双月</t>
+  </si>
+  <si>
+    <t>禾苗</t>
+  </si>
+  <si>
     <t>季度</t>
   </si>
   <si>
-    <t>中级</t>
+    <t>宁波</t>
+  </si>
+  <si>
+    <t>吉利</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>中高级</t>
+  </si>
+  <si>
+    <t>立讯</t>
+  </si>
+  <si>
+    <t>深圳</t>
+  </si>
+  <si>
+    <t>高级</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>东莞</t>
+  </si>
+  <si>
+    <t>资深</t>
+  </si>
+  <si>
+    <t>华勤</t>
+  </si>
+  <si>
+    <t>常州</t>
+  </si>
+  <si>
+    <t>专家</t>
+  </si>
+  <si>
+    <t>宝马</t>
+  </si>
+  <si>
+    <t>苏州</t>
+  </si>
+  <si>
+    <t>京东方</t>
+  </si>
+  <si>
+    <t>无锡</t>
+  </si>
+  <si>
+    <t>美格</t>
+  </si>
+  <si>
+    <t>西安</t>
+  </si>
+  <si>
+    <t>中信信诚</t>
+  </si>
+  <si>
+    <t>合肥</t>
+  </si>
+  <si>
+    <t>北京银行</t>
   </si>
   <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>ITO</t>
-  </si>
-  <si>
-    <t>事业三部</t>
-  </si>
-  <si>
-    <t>汤文杰</t>
-  </si>
-  <si>
-    <t>方龙翔</t>
-  </si>
-  <si>
-    <t>张**</t>
-  </si>
-  <si>
-    <t>诗悦</t>
-  </si>
-  <si>
-    <t>camera tuning工程师</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>事业六部</t>
-  </si>
-  <si>
-    <t>陈搏</t>
-  </si>
-  <si>
-    <t>聂岑楠</t>
-  </si>
-  <si>
-    <t>苏**</t>
-  </si>
-  <si>
-    <t>上海海橘</t>
-  </si>
-  <si>
-    <t>小米</t>
-  </si>
-  <si>
-    <t>路测驾驶员</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>BPO</t>
-  </si>
-  <si>
-    <t>社保缴纳地</t>
-  </si>
-  <si>
-    <t>不缴纳</t>
-  </si>
-  <si>
-    <t>最低社保</t>
-  </si>
-  <si>
-    <t>最低公积金</t>
-  </si>
-  <si>
-    <t>级别</t>
-  </si>
-  <si>
-    <t>回款方式</t>
-  </si>
-  <si>
-    <t>资金费率</t>
-  </si>
-  <si>
-    <t>助理</t>
-  </si>
-  <si>
-    <t>月度</t>
-  </si>
-  <si>
-    <t>安硕</t>
-  </si>
-  <si>
-    <t>半年度</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>初级</t>
-  </si>
-  <si>
-    <t>双月</t>
-  </si>
-  <si>
-    <t>禾苗</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>吉利</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>中高级</t>
-  </si>
-  <si>
-    <t>立讯</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>高级</t>
-  </si>
-  <si>
-    <t>年度</t>
-  </si>
-  <si>
-    <t>东莞</t>
-  </si>
-  <si>
-    <t>资深</t>
-  </si>
-  <si>
-    <t>华勤</t>
-  </si>
-  <si>
-    <t>常州</t>
-  </si>
-  <si>
-    <t>专家</t>
-  </si>
-  <si>
-    <t>宝马</t>
-  </si>
-  <si>
-    <t>苏州</t>
-  </si>
-  <si>
-    <t>京东方</t>
-  </si>
-  <si>
-    <t>无锡</t>
-  </si>
-  <si>
-    <t>美格</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>中信信诚</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>北京银行</t>
-  </si>
-  <si>
     <t>星思半导体</t>
   </si>
   <si>
@@ -438,9 +441,6 @@
   </si>
   <si>
     <t>弋途科技</t>
-  </si>
-  <si>
-    <t>南昌</t>
   </si>
   <si>
     <t>奋达</t>
@@ -2107,7 +2107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="3" width="8.07692307692308" customWidth="1"/>
@@ -2117,6 +2117,7 @@
     <col min="11" max="11" width="7.94230769230769" customWidth="1"/>
     <col min="13" max="13" width="13.9519230769231" customWidth="1"/>
     <col min="14" max="14" width="11.6826923076923" customWidth="1"/>
+    <col min="15" max="15" width="12.9230769230769"/>
     <col min="20" max="20" width="10.2788461538462" customWidth="1"/>
     <col min="22" max="22" width="11.6730769230769" customWidth="1"/>
     <col min="23" max="23" width="11.1153846153846" customWidth="1"/>
@@ -2451,27 +2452,27 @@
         <v>53</v>
       </c>
       <c r="L5" s="58">
-        <v>26500</v>
+        <v>20000</v>
       </c>
       <c r="M5" s="58">
-        <f>L5-O5</f>
-        <v>24719.2</v>
+        <f>L5/1.0672</f>
+        <v>18740.6296851574</v>
       </c>
       <c r="N5" s="58">
         <v>15000</v>
       </c>
       <c r="O5" s="61">
-        <f>L5*0.0672</f>
-        <v>1780.8</v>
+        <f>L5-M5</f>
+        <v>1259.37031484258</v>
       </c>
       <c r="P5" s="62"/>
       <c r="Q5" s="62">
         <f>IF($Q$4="不缴纳",0,VLOOKUP(K5,配置项!A:D,3,0))</f>
-        <v>1207</v>
+        <v>1058</v>
       </c>
       <c r="R5" s="62">
         <f>IF($R$4="不缴纳",0,VLOOKUP(K5,配置项!A:D,4,0))</f>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="S5" s="62">
         <v>200</v>
@@ -2487,28 +2488,28 @@
       </c>
       <c r="W5" s="62">
         <f>IF($W$4="公司承担",VLOOKUP(I5,配置项!J:K,2,0),0)*L5</f>
-        <v>530</v>
+        <v>100</v>
       </c>
       <c r="X5" s="62"/>
       <c r="Y5" s="62">
         <f t="shared" ref="Y5:Y7" si="1">SUM($N5:$X5)</f>
-        <v>19875.1563218391</v>
+        <v>18784.7266366817</v>
       </c>
       <c r="Z5" s="65">
-        <f t="shared" ref="Z5:Z7" si="2">$M5-$Y5</f>
-        <v>4844.04367816092</v>
+        <f>$L5-$Y5</f>
+        <v>1215.27336331834</v>
       </c>
       <c r="AA5" s="66">
-        <f t="shared" ref="AA5:AA7" si="3">$Z5/$M5</f>
-        <v>0.195962801310759</v>
+        <f t="shared" ref="AA5:AA7" si="2">$Z5/$M5</f>
+        <v>0.0648469866666667</v>
       </c>
       <c r="AB5" s="66" t="s">
         <v>54</v>
       </c>
       <c r="AC5" s="72"/>
       <c r="AD5" s="73">
-        <f t="shared" ref="AD5:AD7" si="4">N5/L5</f>
-        <v>0.566037735849057</v>
+        <f t="shared" ref="AD5:AD7" si="3">N5/L5</f>
+        <v>0.75</v>
       </c>
       <c r="AE5" s="74"/>
       <c r="AF5" s="71"/>
@@ -2563,14 +2564,14 @@
         <v>28350</v>
       </c>
       <c r="M6" s="63">
-        <f t="shared" ref="M5:M7" si="5">L6</f>
+        <f t="shared" ref="M5:M7" si="4">L6</f>
         <v>28350</v>
       </c>
       <c r="N6" s="58">
         <v>15000</v>
       </c>
       <c r="O6" s="61">
-        <f t="shared" ref="O5:O7" si="6">M6*0.0672</f>
+        <f t="shared" ref="O5:O7" si="5">M6*0.0672</f>
         <v>1905.12</v>
       </c>
       <c r="P6" s="62"/>
@@ -2604,11 +2605,11 @@
         <v>20478.9763218391</v>
       </c>
       <c r="Z6" s="65">
+        <f t="shared" ref="Z5:Z7" si="6">$M6-$Y6</f>
+        <v>7871.02367816092</v>
+      </c>
+      <c r="AA6" s="66">
         <f t="shared" si="2"/>
-        <v>7871.02367816092</v>
-      </c>
-      <c r="AA6" s="66">
-        <f t="shared" si="3"/>
         <v>0.277637519511849</v>
       </c>
       <c r="AB6" s="66" t="s">
@@ -2616,7 +2617,7 @@
       </c>
       <c r="AC6" s="72"/>
       <c r="AD6" s="73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.529100529100529</v>
       </c>
       <c r="AE6" s="74"/>
@@ -2672,7 +2673,7 @@
         <v>6835.9824</v>
       </c>
       <c r="M7" s="63">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6835.9824</v>
       </c>
       <c r="N7" s="58">
@@ -2712,11 +2713,11 @@
         <v>5427.09766528</v>
       </c>
       <c r="Z7" s="65">
+        <f t="shared" si="6"/>
+        <v>1408.88473472</v>
+      </c>
+      <c r="AA7" s="66">
         <f t="shared" si="2"/>
-        <v>1408.88473472</v>
-      </c>
-      <c r="AA7" s="66">
-        <f t="shared" si="3"/>
         <v>0.206098356063643</v>
       </c>
       <c r="AB7" s="66" t="s">
@@ -2724,7 +2725,7 @@
       </c>
       <c r="AC7" s="72"/>
       <c r="AD7" s="73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.610885130423975</v>
       </c>
       <c r="AE7" s="74"/>
@@ -2875,6 +2876,12 @@
       <c r="AO10" s="79"/>
       <c r="AP10" s="79"/>
       <c r="AQ10" s="79"/>
+    </row>
+    <row r="13" spans="15:15">
+      <c r="O13">
+        <f>L5-O5-N5-Q5-R5-S5-U5-V5-W5</f>
+        <v>1215.27336331834</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3057,17 +3064,17 @@
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="23" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="K2" s="26">
         <v>0.005</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="O2" s="29">
         <v>0.04</v>
@@ -3075,7 +3082,7 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:15">
       <c r="A3" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="10">
         <v>0</v>
@@ -3091,24 +3098,24 @@
         <v>54</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" s="23">
         <v>650</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K3" s="26">
         <v>0.01</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="O3" s="29">
         <v>0.02</v>
@@ -3139,7 +3146,7 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="23" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K4" s="26">
         <v>0.02</v>
@@ -3149,7 +3156,7 @@
         <v>87</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O4" s="29">
         <v>0.04</v>
@@ -3180,7 +3187,7 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K5" s="26">
         <v>0.04</v>
@@ -3190,7 +3197,7 @@
         <v>90</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O5" s="29">
         <v>0.02</v>
@@ -3231,7 +3238,7 @@
         <v>49</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O6" s="29">
         <v>0.01</v>
@@ -3267,7 +3274,7 @@
         <v>96</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O7" s="29">
         <v>0.02</v>
@@ -3303,7 +3310,7 @@
         <v>99</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O8" s="29">
         <v>0.01</v>
@@ -3338,7 +3345,7 @@
         <v>101</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O9" s="29">
         <v>0.02</v>
@@ -3362,7 +3369,7 @@
         <v>70</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="23">
         <v>325</v>
@@ -3372,7 +3379,7 @@
         <v>103</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O10" s="29">
         <v>0.02</v>
@@ -3406,7 +3413,7 @@
         <v>105</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O11" s="29">
         <v>0.005</v>
@@ -3441,7 +3448,7 @@
         <v>107</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O12" s="29">
         <v>0.04</v>
@@ -3449,7 +3456,7 @@
     </row>
     <row r="13" s="2" customFormat="1" spans="1:15">
       <c r="A13" s="9" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="B13" s="10">
         <v>0</v>
@@ -3473,10 +3480,10 @@
       </c>
       <c r="K13" s="5"/>
       <c r="M13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O13" s="29">
         <v>0.01</v>
@@ -3484,7 +3491,7 @@
     </row>
     <row r="14" s="2" customFormat="1" spans="1:15">
       <c r="A14" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="10">
         <v>0</v>
@@ -3508,10 +3515,10 @@
       </c>
       <c r="K14" s="5"/>
       <c r="M14" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O14" s="29">
         <v>0.005</v>
@@ -3519,7 +3526,7 @@
     </row>
     <row r="15" s="2" customFormat="1" spans="1:15">
       <c r="A15" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="10">
         <v>0</v>
@@ -3543,10 +3550,10 @@
       </c>
       <c r="K15" s="5"/>
       <c r="M15" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O15" s="29">
         <v>0.04</v>
@@ -3554,7 +3561,7 @@
     </row>
     <row r="16" s="2" customFormat="1" spans="1:15">
       <c r="A16" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B16" s="10">
         <v>0</v>
@@ -3571,10 +3578,10 @@
       <c r="H16" s="2"/>
       <c r="K16" s="5"/>
       <c r="M16" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O16" s="29">
         <v>0.02</v>
@@ -3582,7 +3589,7 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:15">
       <c r="A17" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="10">
         <v>0</v>
@@ -3600,10 +3607,10 @@
       <c r="H17" s="2"/>
       <c r="K17" s="5"/>
       <c r="M17" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O17" s="29">
         <v>0.04</v>
@@ -3611,7 +3618,7 @@
     </row>
     <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="15" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="B18" s="10">
         <v>0</v>
@@ -3631,7 +3638,7 @@
         <v>118</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O18" s="29">
         <v>0.01</v>
@@ -3658,7 +3665,7 @@
         <v>120</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O19" s="29">
         <v>0.02</v>
@@ -3686,7 +3693,7 @@
         <v>122</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O20" s="29">
         <v>0.01</v>
@@ -3713,7 +3720,7 @@
         <v>124</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O21" s="29">
         <v>0.04</v>
@@ -3740,7 +3747,7 @@
         <v>126</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O22" s="29">
         <v>0.02</v>
@@ -3767,7 +3774,7 @@
         <v>128</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O23" s="29">
         <v>0.01</v>
@@ -3793,7 +3800,7 @@
         <v>130</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O24" s="29">
         <v>0.01</v>
@@ -3819,7 +3826,7 @@
         <v>132</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O25" s="29">
         <v>0.04</v>
@@ -3846,7 +3853,7 @@
         <v>134</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O26" s="29">
         <v>0.02</v>
@@ -3873,7 +3880,7 @@
         <v>136</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O27" s="29">
         <v>0.02</v>
@@ -3900,7 +3907,7 @@
         <v>138</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O28" s="29">
         <v>0.01</v>
@@ -3927,7 +3934,7 @@
         <v>140</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O29" s="29">
         <v>0.02</v>
@@ -3954,7 +3961,7 @@
         <v>142</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O30" s="29">
         <v>0.02</v>
@@ -3981,7 +3988,7 @@
         <v>59</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O31" s="29">
         <v>0.01</v>
@@ -4007,7 +4014,7 @@
         <v>145</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O32" s="29">
         <v>0.01</v>
@@ -4033,7 +4040,7 @@
         <v>147</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O33" s="29">
         <v>0.04</v>
@@ -4059,7 +4066,7 @@
         <v>149</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O34" s="29">
         <v>0.02</v>
@@ -4086,7 +4093,7 @@
         <v>151</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O35" s="29">
         <v>0.01</v>
@@ -4113,7 +4120,7 @@
         <v>153</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O36" s="29">
         <v>0.005</v>
@@ -4139,7 +4146,7 @@
         <v>155</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O37" s="29">
         <v>0.02</v>
@@ -4166,7 +4173,7 @@
         <v>157</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O38" s="29">
         <v>0.005</v>
@@ -4193,7 +4200,7 @@
         <v>159</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O39" s="29">
         <v>0.02</v>
@@ -4219,7 +4226,7 @@
         <v>161</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O40" s="29">
         <v>0.02</v>
@@ -4246,7 +4253,7 @@
         <v>163</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O41" s="29">
         <v>0.02</v>
@@ -4272,7 +4279,7 @@
         <v>165</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O42" s="29">
         <v>0.02</v>
@@ -4298,7 +4305,7 @@
         <v>167</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O43" s="29">
         <v>0.02</v>
@@ -4324,7 +4331,7 @@
         <v>169</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O44" s="29">
         <v>0.01</v>
@@ -4350,7 +4357,7 @@
         <v>67</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O45" s="29">
         <v>0.02</v>
@@ -4376,7 +4383,7 @@
         <v>172</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O46" s="29">
         <v>0.02</v>
@@ -4403,7 +4410,7 @@
         <v>174</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O47" s="29">
         <v>0.005</v>
@@ -4430,7 +4437,7 @@
         <v>176</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O48" s="29">
         <v>0.005</v>
@@ -4457,7 +4464,7 @@
         <v>178</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O49" s="29">
         <v>0.02</v>
@@ -4484,7 +4491,7 @@
         <v>180</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O50" s="29">
         <v>0.02</v>
@@ -4510,7 +4517,7 @@
         <v>181</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O51" s="29">
         <v>0.02</v>
@@ -4536,7 +4543,7 @@
         <v>183</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O52" s="29">
         <v>0.01</v>
@@ -4553,7 +4560,7 @@
         <v>184</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O53" s="29">
         <v>0.01</v>
@@ -4570,7 +4577,7 @@
         <v>185</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O54" s="29">
         <v>0.01</v>
@@ -4587,7 +4594,7 @@
         <v>186</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O55" s="29">
         <v>0.02</v>
@@ -4604,7 +4611,7 @@
         <v>187</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O56" s="29">
         <v>0.01</v>
@@ -4624,7 +4631,7 @@
         <v>189</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O57" s="29">
         <v>0.02</v>
@@ -4644,7 +4651,7 @@
         <v>191</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O58" s="29">
         <v>0.005</v>
@@ -4664,7 +4671,7 @@
         <v>193</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O59" s="29">
         <v>0.005</v>
@@ -4684,7 +4691,7 @@
         <v>195</v>
       </c>
       <c r="N60" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O60" s="29">
         <v>0.04</v>
@@ -4701,7 +4708,7 @@
         <v>196</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O61" s="29">
         <v>0.005</v>
@@ -4722,7 +4729,7 @@
         <v>198</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O62" s="29">
         <v>0.02</v>
@@ -4741,7 +4748,7 @@
         <v>199</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O63" s="29">
         <v>0.01</v>
@@ -4758,7 +4765,7 @@
         <v>200</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O64" s="29">
         <v>0.01</v>
@@ -4775,7 +4782,7 @@
         <v>201</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O65" s="29">
         <v>0.01</v>
@@ -4792,7 +4799,7 @@
         <v>202</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O66" s="29">
         <v>0.02</v>
@@ -4809,7 +4816,7 @@
         <v>203</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O67" s="29">
         <v>0.02</v>
@@ -4826,7 +4833,7 @@
         <v>204</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O68" s="29">
         <v>0.04</v>
@@ -4843,7 +4850,7 @@
         <v>205</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O69" s="29">
         <v>0.02</v>
@@ -4860,7 +4867,7 @@
         <v>206</v>
       </c>
       <c r="N70" s="9" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O70" s="29">
         <v>0.005</v>
@@ -4877,7 +4884,7 @@
         <v>207</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O71" s="29">
         <v>0.02</v>
@@ -4894,7 +4901,7 @@
         <v>208</v>
       </c>
       <c r="N72" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O72" s="29">
         <v>0.01</v>
